--- a/GourmetProject/GameConfig/Datas/unlock.xlsx
+++ b/GourmetProject/GameConfig/Datas/unlock.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unlock_rule" sheetId="1" r:id="Rccfed7a2f8714ae0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unlock_condition" sheetId="2" r:id="R278eb48a4bf34d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unlock_rule" sheetId="1" r:id="Rd70d4abb6e20471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unlock_condition" sheetId="2" r:id="R169264ca82ff4565"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -354,10 +354,8 @@
           <x:t xml:space="preserve">title</x:t>
         </x:is>
       </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">desc</x:t>
-        </x:is>
+      <x:c r="F1" t="str">
+        <x:v>desc</x:v>
       </x:c>
       <x:c r="G1" t="inlineStr">
         <x:is>
@@ -396,10 +394,8 @@
           <x:t xml:space="preserve">结算页展示标题（空则回查目标表）</x:t>
         </x:is>
       </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">结算页展示描述</x:t>
-        </x:is>
+      <x:c r="F2" t="str">
+        <x:v>结算页展示描述</x:v>
       </x:c>
       <x:c r="G2" t="inlineStr">
         <x:is>
@@ -438,10 +434,8 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
+      <x:c r="F3" t="str">
+        <x:v>string</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr">
         <x:is>
@@ -476,7 +470,7 @@
         </x:is>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>装饰品：主厨刀</x:v>
+        <x:v>[term]装饰品[/term]：主厨刀</x:v>
       </x:c>
       <x:c r="G4" t="b">
         <x:v>1</x:v>
@@ -507,7 +501,7 @@
         </x:is>
       </x:c>
       <x:c r="F5" t="str">
-        <x:v>消耗品：加菜券</x:v>
+        <x:v>[term]消耗品[/term]：加菜券</x:v>
       </x:c>
       <x:c r="G5" t="b">
         <x:v>1</x:v>
@@ -538,7 +532,7 @@
         </x:is>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>装饰品：胡椒罐</x:v>
+        <x:v>[term]装饰品[/term]：胡椒罐</x:v>
       </x:c>
       <x:c r="G6" t="b">
         <x:v>1</x:v>
